--- a/src/test/resources/testdata/Modules/01_Login/CompanyLogin/01_DirectLogin.xlsx
+++ b/src/test/resources/testdata/Modules/01_Login/CompanyLogin/01_DirectLogin.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\01_Login\CompanyLogin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29B6E656-B850-46EA-9681-B8896AF7DBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01998338-FFD8-4EEA-A4E2-18E14FFCDF1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -245,7 +258,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -428,6 +441,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -632,7 +651,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -643,6 +662,7 @@
     <xf numFmtId="49" fontId="13" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="13" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="13" fillId="33" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="18" fillId="34" borderId="10" xfId="42" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1084,7 +1104,7 @@
       <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="H2" s="3" t="s">

--- a/src/test/resources/testdata/Modules/01_Login/CompanyLogin/01_DirectLogin.xlsx
+++ b/src/test/resources/testdata/Modules/01_Login/CompanyLogin/01_DirectLogin.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\01_Login\CompanyLogin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01998338-FFD8-4EEA-A4E2-18E14FFCDF1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527618F2-1412-4D61-9F0C-A88B6CDCBD73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -62,9 +62,6 @@
     <t>MODULE_NAME</t>
   </si>
   <si>
-    <t>2601000018</t>
-  </si>
-  <si>
     <t>bandhaninftest</t>
   </si>
   <si>
@@ -104,6 +101,9 @@
   </si>
   <si>
     <t>01_CompanyLogin</t>
+  </si>
+  <si>
+    <t>2602000005</t>
   </si>
 </sst>
 </file>
@@ -651,7 +651,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -663,6 +663,9 @@
     <xf numFmtId="49" fontId="13" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="13" fillId="33" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="18" fillId="34" borderId="10" xfId="42" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1073,10 +1076,10 @@
         <v>2</v>
       </c>
       <c r="G1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>13</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>14</v>
       </c>
       <c r="I1" s="7" t="s">
         <v>3</v>
@@ -1086,29 +1089,29 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="217.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="G2" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="1" t="s">
